--- a/AzureStandard202602/Summaries.xlsx
+++ b/AzureStandard202602/Summaries.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\MouriNaruto\BenchmarkResultArchive\AzureStandard202602\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D97D6C3-206D-4A97-9CBC-86402BD52F82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6C295BA-AD8E-4166-8741-06C1F12E24EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{31936A19-3E87-422A-B606-524D582BFEC0}"/>
+    <workbookView xWindow="11160" yWindow="2604" windowWidth="23040" windowHeight="12120" activeTab="2" xr2:uid="{31936A19-3E87-422A-B606-524D582BFEC0}"/>
   </bookViews>
   <sheets>
     <sheet name="benchncnn" sheetId="2" r:id="rId1"/>
     <sheet name="7-Zip Benchmark" sheetId="3" r:id="rId2"/>
+    <sheet name="SPEC CPU 2006" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="79">
   <si>
     <t>D64as v7</t>
   </si>
@@ -253,6 +254,62 @@
     <t>ICC, Zen 4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>CINT2006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFP2006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CINT2006rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CFP2006rate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Peak</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D64s v6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-march=native</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-march=native -mprefer-vector-width=512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>-march=sapphirerapids -mprefer-vector-width=512</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D64as v7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Base Optimization Flags</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>copies=64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -283,7 +340,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -594,13 +651,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -652,19 +737,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -676,31 +794,88 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1044,64 +1219,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="20"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="25" t="s">
+      <c r="D1" s="32"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="25" t="s">
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="27"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
     </row>
     <row r="2" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="25" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="25" t="s">
+      <c r="G2" s="30"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="J2" s="26"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="25" t="s">
+      <c r="J2" s="30"/>
+      <c r="K2" s="31"/>
+      <c r="L2" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="25" t="s">
+      <c r="M2" s="30"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="27"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="31"/>
     </row>
     <row r="3" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="13" t="s">
         <v>2</v>
       </c>
@@ -1149,7 +1324,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="16">
+      <c r="A4" s="20">
         <v>1</v>
       </c>
       <c r="B4" s="11" t="s">
@@ -1202,7 +1377,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="8" t="s">
         <v>5</v>
       </c>
@@ -1253,7 +1428,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
+      <c r="A6" s="21"/>
       <c r="B6" s="8" t="s">
         <v>6</v>
       </c>
@@ -1304,7 +1479,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A7" s="17"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
@@ -1355,7 +1530,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A8" s="17"/>
+      <c r="A8" s="21"/>
       <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1406,7 +1581,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
+      <c r="A9" s="21"/>
       <c r="B9" s="8" t="s">
         <v>9</v>
       </c>
@@ -1457,7 +1632,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="8" t="s">
         <v>10</v>
       </c>
@@ -1508,7 +1683,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
@@ -1559,7 +1734,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="8" t="s">
         <v>12</v>
       </c>
@@ -1610,7 +1785,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="8" t="s">
         <v>13</v>
       </c>
@@ -1661,7 +1836,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
@@ -1712,7 +1887,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A15" s="17"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="8" t="s">
         <v>15</v>
       </c>
@@ -1763,7 +1938,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="8" t="s">
         <v>16</v>
       </c>
@@ -1814,7 +1989,7 @@
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="8" t="s">
         <v>17</v>
       </c>
@@ -1865,7 +2040,7 @@
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="8" t="s">
         <v>18</v>
       </c>
@@ -1916,7 +2091,7 @@
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A19" s="17"/>
+      <c r="A19" s="21"/>
       <c r="B19" s="8" t="s">
         <v>19</v>
       </c>
@@ -1967,7 +2142,7 @@
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
+      <c r="A20" s="21"/>
       <c r="B20" s="8" t="s">
         <v>20</v>
       </c>
@@ -2018,7 +2193,7 @@
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
+      <c r="A21" s="21"/>
       <c r="B21" s="8" t="s">
         <v>21</v>
       </c>
@@ -2069,7 +2244,7 @@
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
+      <c r="A22" s="21"/>
       <c r="B22" s="8" t="s">
         <v>22</v>
       </c>
@@ -2120,7 +2295,7 @@
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="17"/>
+      <c r="A23" s="21"/>
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
@@ -2171,7 +2346,7 @@
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
+      <c r="A24" s="21"/>
       <c r="B24" s="8" t="s">
         <v>24</v>
       </c>
@@ -2222,7 +2397,7 @@
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
+      <c r="A25" s="21"/>
       <c r="B25" s="8" t="s">
         <v>25</v>
       </c>
@@ -2273,7 +2448,7 @@
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
+      <c r="A26" s="21"/>
       <c r="B26" s="8" t="s">
         <v>26</v>
       </c>
@@ -2324,7 +2499,7 @@
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A27" s="17"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="8" t="s">
         <v>27</v>
       </c>
@@ -2375,7 +2550,7 @@
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
+      <c r="A28" s="21"/>
       <c r="B28" s="8" t="s">
         <v>28</v>
       </c>
@@ -2426,7 +2601,7 @@
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
+      <c r="A29" s="21"/>
       <c r="B29" s="8" t="s">
         <v>29</v>
       </c>
@@ -2477,7 +2652,7 @@
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
+      <c r="A30" s="21"/>
       <c r="B30" s="8" t="s">
         <v>30</v>
       </c>
@@ -2528,7 +2703,7 @@
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A31" s="17"/>
+      <c r="A31" s="21"/>
       <c r="B31" s="8" t="s">
         <v>31</v>
       </c>
@@ -2579,7 +2754,7 @@
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A32" s="17"/>
+      <c r="A32" s="21"/>
       <c r="B32" s="8" t="s">
         <v>32</v>
       </c>
@@ -2630,7 +2805,7 @@
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
+      <c r="A33" s="21"/>
       <c r="B33" s="8" t="s">
         <v>33</v>
       </c>
@@ -2681,7 +2856,7 @@
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
+      <c r="A34" s="21"/>
       <c r="B34" s="8" t="s">
         <v>34</v>
       </c>
@@ -2732,7 +2907,7 @@
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A35" s="17"/>
+      <c r="A35" s="21"/>
       <c r="B35" s="8" t="s">
         <v>35</v>
       </c>
@@ -2783,7 +2958,7 @@
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
+      <c r="A36" s="21"/>
       <c r="B36" s="8" t="s">
         <v>36</v>
       </c>
@@ -2834,7 +3009,7 @@
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
+      <c r="A37" s="21"/>
       <c r="B37" s="8" t="s">
         <v>37</v>
       </c>
@@ -2885,7 +3060,7 @@
       </c>
     </row>
     <row r="38" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="18"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="9" t="s">
         <v>38</v>
       </c>
@@ -2936,7 +3111,7 @@
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A39" s="16">
+      <c r="A39" s="20">
         <v>2</v>
       </c>
       <c r="B39" s="11" t="s">
@@ -2989,7 +3164,7 @@
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
+      <c r="A40" s="21"/>
       <c r="B40" s="8" t="s">
         <v>5</v>
       </c>
@@ -3040,7 +3215,7 @@
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
+      <c r="A41" s="21"/>
       <c r="B41" s="8" t="s">
         <v>6</v>
       </c>
@@ -3091,7 +3266,7 @@
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
+      <c r="A42" s="21"/>
       <c r="B42" s="8" t="s">
         <v>7</v>
       </c>
@@ -3142,7 +3317,7 @@
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A43" s="17"/>
+      <c r="A43" s="21"/>
       <c r="B43" s="8" t="s">
         <v>8</v>
       </c>
@@ -3193,7 +3368,7 @@
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
+      <c r="A44" s="21"/>
       <c r="B44" s="8" t="s">
         <v>9</v>
       </c>
@@ -3244,7 +3419,7 @@
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
+      <c r="A45" s="21"/>
       <c r="B45" s="8" t="s">
         <v>10</v>
       </c>
@@ -3295,7 +3470,7 @@
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
+      <c r="A46" s="21"/>
       <c r="B46" s="8" t="s">
         <v>11</v>
       </c>
@@ -3346,7 +3521,7 @@
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A47" s="17"/>
+      <c r="A47" s="21"/>
       <c r="B47" s="8" t="s">
         <v>12</v>
       </c>
@@ -3397,7 +3572,7 @@
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
+      <c r="A48" s="21"/>
       <c r="B48" s="8" t="s">
         <v>13</v>
       </c>
@@ -3448,7 +3623,7 @@
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
+      <c r="A49" s="21"/>
       <c r="B49" s="8" t="s">
         <v>14</v>
       </c>
@@ -3499,7 +3674,7 @@
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
+      <c r="A50" s="21"/>
       <c r="B50" s="8" t="s">
         <v>15</v>
       </c>
@@ -3550,7 +3725,7 @@
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A51" s="17"/>
+      <c r="A51" s="21"/>
       <c r="B51" s="8" t="s">
         <v>16</v>
       </c>
@@ -3601,7 +3776,7 @@
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="8" t="s">
         <v>17</v>
       </c>
@@ -3652,7 +3827,7 @@
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="8" t="s">
         <v>18</v>
       </c>
@@ -3703,7 +3878,7 @@
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="8" t="s">
         <v>19</v>
       </c>
@@ -3754,7 +3929,7 @@
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A55" s="17"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="8" t="s">
         <v>20</v>
       </c>
@@ -3805,7 +3980,7 @@
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A56" s="17"/>
+      <c r="A56" s="21"/>
       <c r="B56" s="8" t="s">
         <v>21</v>
       </c>
@@ -3856,7 +4031,7 @@
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A57" s="17"/>
+      <c r="A57" s="21"/>
       <c r="B57" s="8" t="s">
         <v>22</v>
       </c>
@@ -3907,7 +4082,7 @@
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A58" s="17"/>
+      <c r="A58" s="21"/>
       <c r="B58" s="8" t="s">
         <v>23</v>
       </c>
@@ -3958,7 +4133,7 @@
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A59" s="17"/>
+      <c r="A59" s="21"/>
       <c r="B59" s="8" t="s">
         <v>24</v>
       </c>
@@ -4009,7 +4184,7 @@
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A60" s="17"/>
+      <c r="A60" s="21"/>
       <c r="B60" s="8" t="s">
         <v>25</v>
       </c>
@@ -4060,7 +4235,7 @@
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A61" s="17"/>
+      <c r="A61" s="21"/>
       <c r="B61" s="8" t="s">
         <v>26</v>
       </c>
@@ -4111,7 +4286,7 @@
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A62" s="17"/>
+      <c r="A62" s="21"/>
       <c r="B62" s="8" t="s">
         <v>27</v>
       </c>
@@ -4162,7 +4337,7 @@
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
+      <c r="A63" s="21"/>
       <c r="B63" s="8" t="s">
         <v>28</v>
       </c>
@@ -4213,7 +4388,7 @@
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A64" s="17"/>
+      <c r="A64" s="21"/>
       <c r="B64" s="8" t="s">
         <v>29</v>
       </c>
@@ -4264,7 +4439,7 @@
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
+      <c r="A65" s="21"/>
       <c r="B65" s="8" t="s">
         <v>30</v>
       </c>
@@ -4315,7 +4490,7 @@
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
+      <c r="A66" s="21"/>
       <c r="B66" s="8" t="s">
         <v>31</v>
       </c>
@@ -4366,7 +4541,7 @@
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A67" s="17"/>
+      <c r="A67" s="21"/>
       <c r="B67" s="8" t="s">
         <v>32</v>
       </c>
@@ -4417,7 +4592,7 @@
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A68" s="17"/>
+      <c r="A68" s="21"/>
       <c r="B68" s="8" t="s">
         <v>33</v>
       </c>
@@ -4468,7 +4643,7 @@
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
+      <c r="A69" s="21"/>
       <c r="B69" s="8" t="s">
         <v>34</v>
       </c>
@@ -4519,7 +4694,7 @@
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A70" s="17"/>
+      <c r="A70" s="21"/>
       <c r="B70" s="8" t="s">
         <v>35</v>
       </c>
@@ -4570,7 +4745,7 @@
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
+      <c r="A71" s="21"/>
       <c r="B71" s="8" t="s">
         <v>36</v>
       </c>
@@ -4621,7 +4796,7 @@
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
+      <c r="A72" s="21"/>
       <c r="B72" s="8" t="s">
         <v>37</v>
       </c>
@@ -4672,7 +4847,7 @@
       </c>
     </row>
     <row r="73" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="18"/>
+      <c r="A73" s="22"/>
       <c r="B73" s="9" t="s">
         <v>38</v>
       </c>
@@ -4723,7 +4898,7 @@
       </c>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A74" s="16">
+      <c r="A74" s="20">
         <v>4</v>
       </c>
       <c r="B74" s="11" t="s">
@@ -4776,7 +4951,7 @@
       </c>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
+      <c r="A75" s="21"/>
       <c r="B75" s="8" t="s">
         <v>5</v>
       </c>
@@ -4827,7 +5002,7 @@
       </c>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="8" t="s">
         <v>6</v>
       </c>
@@ -4878,7 +5053,7 @@
       </c>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="8" t="s">
         <v>7</v>
       </c>
@@ -4929,7 +5104,7 @@
       </c>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="8" t="s">
         <v>8</v>
       </c>
@@ -4980,7 +5155,7 @@
       </c>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="8" t="s">
         <v>9</v>
       </c>
@@ -5031,7 +5206,7 @@
       </c>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="8" t="s">
         <v>10</v>
       </c>
@@ -5082,7 +5257,7 @@
       </c>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A81" s="17"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="8" t="s">
         <v>11</v>
       </c>
@@ -5133,7 +5308,7 @@
       </c>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A82" s="17"/>
+      <c r="A82" s="21"/>
       <c r="B82" s="8" t="s">
         <v>12</v>
       </c>
@@ -5184,7 +5359,7 @@
       </c>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A83" s="17"/>
+      <c r="A83" s="21"/>
       <c r="B83" s="8" t="s">
         <v>13</v>
       </c>
@@ -5235,7 +5410,7 @@
       </c>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A84" s="17"/>
+      <c r="A84" s="21"/>
       <c r="B84" s="8" t="s">
         <v>14</v>
       </c>
@@ -5286,7 +5461,7 @@
       </c>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A85" s="17"/>
+      <c r="A85" s="21"/>
       <c r="B85" s="8" t="s">
         <v>15</v>
       </c>
@@ -5337,7 +5512,7 @@
       </c>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A86" s="17"/>
+      <c r="A86" s="21"/>
       <c r="B86" s="8" t="s">
         <v>16</v>
       </c>
@@ -5388,7 +5563,7 @@
       </c>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A87" s="17"/>
+      <c r="A87" s="21"/>
       <c r="B87" s="8" t="s">
         <v>17</v>
       </c>
@@ -5439,7 +5614,7 @@
       </c>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A88" s="17"/>
+      <c r="A88" s="21"/>
       <c r="B88" s="8" t="s">
         <v>18</v>
       </c>
@@ -5490,7 +5665,7 @@
       </c>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A89" s="17"/>
+      <c r="A89" s="21"/>
       <c r="B89" s="8" t="s">
         <v>19</v>
       </c>
@@ -5541,7 +5716,7 @@
       </c>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A90" s="17"/>
+      <c r="A90" s="21"/>
       <c r="B90" s="8" t="s">
         <v>20</v>
       </c>
@@ -5592,7 +5767,7 @@
       </c>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A91" s="17"/>
+      <c r="A91" s="21"/>
       <c r="B91" s="8" t="s">
         <v>21</v>
       </c>
@@ -5643,7 +5818,7 @@
       </c>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A92" s="17"/>
+      <c r="A92" s="21"/>
       <c r="B92" s="8" t="s">
         <v>22</v>
       </c>
@@ -5694,7 +5869,7 @@
       </c>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A93" s="17"/>
+      <c r="A93" s="21"/>
       <c r="B93" s="8" t="s">
         <v>23</v>
       </c>
@@ -5745,7 +5920,7 @@
       </c>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A94" s="17"/>
+      <c r="A94" s="21"/>
       <c r="B94" s="8" t="s">
         <v>24</v>
       </c>
@@ -5796,7 +5971,7 @@
       </c>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A95" s="17"/>
+      <c r="A95" s="21"/>
       <c r="B95" s="8" t="s">
         <v>25</v>
       </c>
@@ -5847,7 +6022,7 @@
       </c>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A96" s="17"/>
+      <c r="A96" s="21"/>
       <c r="B96" s="8" t="s">
         <v>26</v>
       </c>
@@ -5898,7 +6073,7 @@
       </c>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A97" s="17"/>
+      <c r="A97" s="21"/>
       <c r="B97" s="8" t="s">
         <v>27</v>
       </c>
@@ -5949,7 +6124,7 @@
       </c>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A98" s="17"/>
+      <c r="A98" s="21"/>
       <c r="B98" s="8" t="s">
         <v>28</v>
       </c>
@@ -6000,7 +6175,7 @@
       </c>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A99" s="17"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="8" t="s">
         <v>29</v>
       </c>
@@ -6051,7 +6226,7 @@
       </c>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A100" s="17"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="8" t="s">
         <v>30</v>
       </c>
@@ -6102,7 +6277,7 @@
       </c>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A101" s="17"/>
+      <c r="A101" s="21"/>
       <c r="B101" s="8" t="s">
         <v>31</v>
       </c>
@@ -6153,7 +6328,7 @@
       </c>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A102" s="17"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="8" t="s">
         <v>32</v>
       </c>
@@ -6204,7 +6379,7 @@
       </c>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A103" s="17"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="8" t="s">
         <v>33</v>
       </c>
@@ -6255,7 +6430,7 @@
       </c>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A104" s="17"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="8" t="s">
         <v>34</v>
       </c>
@@ -6306,7 +6481,7 @@
       </c>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A105" s="17"/>
+      <c r="A105" s="21"/>
       <c r="B105" s="8" t="s">
         <v>35</v>
       </c>
@@ -6357,7 +6532,7 @@
       </c>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A106" s="17"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="8" t="s">
         <v>36</v>
       </c>
@@ -6408,7 +6583,7 @@
       </c>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A107" s="17"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="8" t="s">
         <v>37</v>
       </c>
@@ -6459,7 +6634,7 @@
       </c>
     </row>
     <row r="108" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="18"/>
+      <c r="A108" s="22"/>
       <c r="B108" s="9" t="s">
         <v>38</v>
       </c>
@@ -6510,7 +6685,7 @@
       </c>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A109" s="16">
+      <c r="A109" s="20">
         <v>8</v>
       </c>
       <c r="B109" s="11" t="s">
@@ -6563,7 +6738,7 @@
       </c>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A110" s="17"/>
+      <c r="A110" s="21"/>
       <c r="B110" s="8" t="s">
         <v>5</v>
       </c>
@@ -6614,7 +6789,7 @@
       </c>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A111" s="17"/>
+      <c r="A111" s="21"/>
       <c r="B111" s="8" t="s">
         <v>6</v>
       </c>
@@ -6665,7 +6840,7 @@
       </c>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A112" s="17"/>
+      <c r="A112" s="21"/>
       <c r="B112" s="8" t="s">
         <v>7</v>
       </c>
@@ -6716,7 +6891,7 @@
       </c>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A113" s="17"/>
+      <c r="A113" s="21"/>
       <c r="B113" s="8" t="s">
         <v>8</v>
       </c>
@@ -6767,7 +6942,7 @@
       </c>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A114" s="17"/>
+      <c r="A114" s="21"/>
       <c r="B114" s="8" t="s">
         <v>9</v>
       </c>
@@ -6818,7 +6993,7 @@
       </c>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A115" s="17"/>
+      <c r="A115" s="21"/>
       <c r="B115" s="8" t="s">
         <v>10</v>
       </c>
@@ -6869,7 +7044,7 @@
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A116" s="17"/>
+      <c r="A116" s="21"/>
       <c r="B116" s="8" t="s">
         <v>11</v>
       </c>
@@ -6920,7 +7095,7 @@
       </c>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A117" s="17"/>
+      <c r="A117" s="21"/>
       <c r="B117" s="8" t="s">
         <v>12</v>
       </c>
@@ -6971,7 +7146,7 @@
       </c>
     </row>
     <row r="118" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A118" s="17"/>
+      <c r="A118" s="21"/>
       <c r="B118" s="8" t="s">
         <v>13</v>
       </c>
@@ -7022,7 +7197,7 @@
       </c>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A119" s="17"/>
+      <c r="A119" s="21"/>
       <c r="B119" s="8" t="s">
         <v>14</v>
       </c>
@@ -7073,7 +7248,7 @@
       </c>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A120" s="17"/>
+      <c r="A120" s="21"/>
       <c r="B120" s="8" t="s">
         <v>15</v>
       </c>
@@ -7124,7 +7299,7 @@
       </c>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A121" s="17"/>
+      <c r="A121" s="21"/>
       <c r="B121" s="8" t="s">
         <v>16</v>
       </c>
@@ -7175,7 +7350,7 @@
       </c>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A122" s="17"/>
+      <c r="A122" s="21"/>
       <c r="B122" s="8" t="s">
         <v>17</v>
       </c>
@@ -7226,7 +7401,7 @@
       </c>
     </row>
     <row r="123" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A123" s="17"/>
+      <c r="A123" s="21"/>
       <c r="B123" s="8" t="s">
         <v>18</v>
       </c>
@@ -7277,7 +7452,7 @@
       </c>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A124" s="17"/>
+      <c r="A124" s="21"/>
       <c r="B124" s="8" t="s">
         <v>19</v>
       </c>
@@ -7328,7 +7503,7 @@
       </c>
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A125" s="17"/>
+      <c r="A125" s="21"/>
       <c r="B125" s="8" t="s">
         <v>20</v>
       </c>
@@ -7379,7 +7554,7 @@
       </c>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A126" s="17"/>
+      <c r="A126" s="21"/>
       <c r="B126" s="8" t="s">
         <v>21</v>
       </c>
@@ -7430,7 +7605,7 @@
       </c>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A127" s="17"/>
+      <c r="A127" s="21"/>
       <c r="B127" s="8" t="s">
         <v>22</v>
       </c>
@@ -7481,7 +7656,7 @@
       </c>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A128" s="17"/>
+      <c r="A128" s="21"/>
       <c r="B128" s="8" t="s">
         <v>23</v>
       </c>
@@ -7532,7 +7707,7 @@
       </c>
     </row>
     <row r="129" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A129" s="17"/>
+      <c r="A129" s="21"/>
       <c r="B129" s="8" t="s">
         <v>24</v>
       </c>
@@ -7583,7 +7758,7 @@
       </c>
     </row>
     <row r="130" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A130" s="17"/>
+      <c r="A130" s="21"/>
       <c r="B130" s="8" t="s">
         <v>25</v>
       </c>
@@ -7634,7 +7809,7 @@
       </c>
     </row>
     <row r="131" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A131" s="17"/>
+      <c r="A131" s="21"/>
       <c r="B131" s="8" t="s">
         <v>26</v>
       </c>
@@ -7685,7 +7860,7 @@
       </c>
     </row>
     <row r="132" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A132" s="17"/>
+      <c r="A132" s="21"/>
       <c r="B132" s="8" t="s">
         <v>27</v>
       </c>
@@ -7736,7 +7911,7 @@
       </c>
     </row>
     <row r="133" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A133" s="17"/>
+      <c r="A133" s="21"/>
       <c r="B133" s="8" t="s">
         <v>28</v>
       </c>
@@ -7787,7 +7962,7 @@
       </c>
     </row>
     <row r="134" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A134" s="17"/>
+      <c r="A134" s="21"/>
       <c r="B134" s="8" t="s">
         <v>29</v>
       </c>
@@ -7838,7 +8013,7 @@
       </c>
     </row>
     <row r="135" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A135" s="17"/>
+      <c r="A135" s="21"/>
       <c r="B135" s="8" t="s">
         <v>30</v>
       </c>
@@ -7889,7 +8064,7 @@
       </c>
     </row>
     <row r="136" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A136" s="17"/>
+      <c r="A136" s="21"/>
       <c r="B136" s="8" t="s">
         <v>31</v>
       </c>
@@ -7940,7 +8115,7 @@
       </c>
     </row>
     <row r="137" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A137" s="17"/>
+      <c r="A137" s="21"/>
       <c r="B137" s="8" t="s">
         <v>32</v>
       </c>
@@ -7991,7 +8166,7 @@
       </c>
     </row>
     <row r="138" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A138" s="17"/>
+      <c r="A138" s="21"/>
       <c r="B138" s="8" t="s">
         <v>33</v>
       </c>
@@ -8042,7 +8217,7 @@
       </c>
     </row>
     <row r="139" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A139" s="17"/>
+      <c r="A139" s="21"/>
       <c r="B139" s="8" t="s">
         <v>34</v>
       </c>
@@ -8093,7 +8268,7 @@
       </c>
     </row>
     <row r="140" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A140" s="17"/>
+      <c r="A140" s="21"/>
       <c r="B140" s="8" t="s">
         <v>35</v>
       </c>
@@ -8144,7 +8319,7 @@
       </c>
     </row>
     <row r="141" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A141" s="17"/>
+      <c r="A141" s="21"/>
       <c r="B141" s="8" t="s">
         <v>36</v>
       </c>
@@ -8195,7 +8370,7 @@
       </c>
     </row>
     <row r="142" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A142" s="17"/>
+      <c r="A142" s="21"/>
       <c r="B142" s="8" t="s">
         <v>37</v>
       </c>
@@ -8246,7 +8421,7 @@
       </c>
     </row>
     <row r="143" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="18"/>
+      <c r="A143" s="22"/>
       <c r="B143" s="9" t="s">
         <v>38</v>
       </c>
@@ -8297,7 +8472,7 @@
       </c>
     </row>
     <row r="144" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A144" s="16">
+      <c r="A144" s="20">
         <v>16</v>
       </c>
       <c r="B144" s="11" t="s">
@@ -8350,7 +8525,7 @@
       </c>
     </row>
     <row r="145" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A145" s="17"/>
+      <c r="A145" s="21"/>
       <c r="B145" s="8" t="s">
         <v>5</v>
       </c>
@@ -8401,7 +8576,7 @@
       </c>
     </row>
     <row r="146" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A146" s="17"/>
+      <c r="A146" s="21"/>
       <c r="B146" s="8" t="s">
         <v>6</v>
       </c>
@@ -8452,7 +8627,7 @@
       </c>
     </row>
     <row r="147" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A147" s="17"/>
+      <c r="A147" s="21"/>
       <c r="B147" s="8" t="s">
         <v>7</v>
       </c>
@@ -8503,7 +8678,7 @@
       </c>
     </row>
     <row r="148" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A148" s="17"/>
+      <c r="A148" s="21"/>
       <c r="B148" s="8" t="s">
         <v>8</v>
       </c>
@@ -8554,7 +8729,7 @@
       </c>
     </row>
     <row r="149" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A149" s="17"/>
+      <c r="A149" s="21"/>
       <c r="B149" s="8" t="s">
         <v>9</v>
       </c>
@@ -8605,7 +8780,7 @@
       </c>
     </row>
     <row r="150" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A150" s="17"/>
+      <c r="A150" s="21"/>
       <c r="B150" s="8" t="s">
         <v>10</v>
       </c>
@@ -8656,7 +8831,7 @@
       </c>
     </row>
     <row r="151" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A151" s="17"/>
+      <c r="A151" s="21"/>
       <c r="B151" s="8" t="s">
         <v>11</v>
       </c>
@@ -8707,7 +8882,7 @@
       </c>
     </row>
     <row r="152" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A152" s="17"/>
+      <c r="A152" s="21"/>
       <c r="B152" s="8" t="s">
         <v>12</v>
       </c>
@@ -8758,7 +8933,7 @@
       </c>
     </row>
     <row r="153" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A153" s="17"/>
+      <c r="A153" s="21"/>
       <c r="B153" s="8" t="s">
         <v>13</v>
       </c>
@@ -8809,7 +8984,7 @@
       </c>
     </row>
     <row r="154" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A154" s="17"/>
+      <c r="A154" s="21"/>
       <c r="B154" s="8" t="s">
         <v>14</v>
       </c>
@@ -8860,7 +9035,7 @@
       </c>
     </row>
     <row r="155" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A155" s="17"/>
+      <c r="A155" s="21"/>
       <c r="B155" s="8" t="s">
         <v>15</v>
       </c>
@@ -8911,7 +9086,7 @@
       </c>
     </row>
     <row r="156" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A156" s="17"/>
+      <c r="A156" s="21"/>
       <c r="B156" s="8" t="s">
         <v>16</v>
       </c>
@@ -8962,7 +9137,7 @@
       </c>
     </row>
     <row r="157" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A157" s="17"/>
+      <c r="A157" s="21"/>
       <c r="B157" s="8" t="s">
         <v>17</v>
       </c>
@@ -9013,7 +9188,7 @@
       </c>
     </row>
     <row r="158" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A158" s="17"/>
+      <c r="A158" s="21"/>
       <c r="B158" s="8" t="s">
         <v>18</v>
       </c>
@@ -9064,7 +9239,7 @@
       </c>
     </row>
     <row r="159" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A159" s="17"/>
+      <c r="A159" s="21"/>
       <c r="B159" s="8" t="s">
         <v>19</v>
       </c>
@@ -9115,7 +9290,7 @@
       </c>
     </row>
     <row r="160" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A160" s="17"/>
+      <c r="A160" s="21"/>
       <c r="B160" s="8" t="s">
         <v>20</v>
       </c>
@@ -9166,7 +9341,7 @@
       </c>
     </row>
     <row r="161" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A161" s="17"/>
+      <c r="A161" s="21"/>
       <c r="B161" s="8" t="s">
         <v>21</v>
       </c>
@@ -9217,7 +9392,7 @@
       </c>
     </row>
     <row r="162" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A162" s="17"/>
+      <c r="A162" s="21"/>
       <c r="B162" s="8" t="s">
         <v>22</v>
       </c>
@@ -9268,7 +9443,7 @@
       </c>
     </row>
     <row r="163" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A163" s="17"/>
+      <c r="A163" s="21"/>
       <c r="B163" s="8" t="s">
         <v>23</v>
       </c>
@@ -9319,7 +9494,7 @@
       </c>
     </row>
     <row r="164" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A164" s="17"/>
+      <c r="A164" s="21"/>
       <c r="B164" s="8" t="s">
         <v>24</v>
       </c>
@@ -9370,7 +9545,7 @@
       </c>
     </row>
     <row r="165" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A165" s="17"/>
+      <c r="A165" s="21"/>
       <c r="B165" s="8" t="s">
         <v>25</v>
       </c>
@@ -9421,7 +9596,7 @@
       </c>
     </row>
     <row r="166" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A166" s="17"/>
+      <c r="A166" s="21"/>
       <c r="B166" s="8" t="s">
         <v>26</v>
       </c>
@@ -9472,7 +9647,7 @@
       </c>
     </row>
     <row r="167" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A167" s="17"/>
+      <c r="A167" s="21"/>
       <c r="B167" s="8" t="s">
         <v>27</v>
       </c>
@@ -9523,7 +9698,7 @@
       </c>
     </row>
     <row r="168" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A168" s="17"/>
+      <c r="A168" s="21"/>
       <c r="B168" s="8" t="s">
         <v>28</v>
       </c>
@@ -9574,7 +9749,7 @@
       </c>
     </row>
     <row r="169" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A169" s="17"/>
+      <c r="A169" s="21"/>
       <c r="B169" s="8" t="s">
         <v>29</v>
       </c>
@@ -9625,7 +9800,7 @@
       </c>
     </row>
     <row r="170" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A170" s="17"/>
+      <c r="A170" s="21"/>
       <c r="B170" s="8" t="s">
         <v>30</v>
       </c>
@@ -9676,7 +9851,7 @@
       </c>
     </row>
     <row r="171" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A171" s="17"/>
+      <c r="A171" s="21"/>
       <c r="B171" s="8" t="s">
         <v>31</v>
       </c>
@@ -9727,7 +9902,7 @@
       </c>
     </row>
     <row r="172" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A172" s="17"/>
+      <c r="A172" s="21"/>
       <c r="B172" s="8" t="s">
         <v>32</v>
       </c>
@@ -9778,7 +9953,7 @@
       </c>
     </row>
     <row r="173" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A173" s="17"/>
+      <c r="A173" s="21"/>
       <c r="B173" s="8" t="s">
         <v>33</v>
       </c>
@@ -9829,7 +10004,7 @@
       </c>
     </row>
     <row r="174" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A174" s="17"/>
+      <c r="A174" s="21"/>
       <c r="B174" s="8" t="s">
         <v>34</v>
       </c>
@@ -9880,7 +10055,7 @@
       </c>
     </row>
     <row r="175" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A175" s="17"/>
+      <c r="A175" s="21"/>
       <c r="B175" s="8" t="s">
         <v>35</v>
       </c>
@@ -9931,7 +10106,7 @@
       </c>
     </row>
     <row r="176" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A176" s="17"/>
+      <c r="A176" s="21"/>
       <c r="B176" s="8" t="s">
         <v>36</v>
       </c>
@@ -9982,7 +10157,7 @@
       </c>
     </row>
     <row r="177" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A177" s="17"/>
+      <c r="A177" s="21"/>
       <c r="B177" s="8" t="s">
         <v>37</v>
       </c>
@@ -10033,7 +10208,7 @@
       </c>
     </row>
     <row r="178" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="18"/>
+      <c r="A178" s="22"/>
       <c r="B178" s="9" t="s">
         <v>38</v>
       </c>
@@ -10084,7 +10259,7 @@
       </c>
     </row>
     <row r="179" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A179" s="16">
+      <c r="A179" s="20">
         <v>32</v>
       </c>
       <c r="B179" s="11" t="s">
@@ -10137,7 +10312,7 @@
       </c>
     </row>
     <row r="180" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A180" s="17"/>
+      <c r="A180" s="21"/>
       <c r="B180" s="8" t="s">
         <v>5</v>
       </c>
@@ -10188,7 +10363,7 @@
       </c>
     </row>
     <row r="181" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A181" s="17"/>
+      <c r="A181" s="21"/>
       <c r="B181" s="8" t="s">
         <v>6</v>
       </c>
@@ -10239,7 +10414,7 @@
       </c>
     </row>
     <row r="182" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A182" s="17"/>
+      <c r="A182" s="21"/>
       <c r="B182" s="8" t="s">
         <v>7</v>
       </c>
@@ -10290,7 +10465,7 @@
       </c>
     </row>
     <row r="183" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A183" s="17"/>
+      <c r="A183" s="21"/>
       <c r="B183" s="8" t="s">
         <v>8</v>
       </c>
@@ -10341,7 +10516,7 @@
       </c>
     </row>
     <row r="184" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A184" s="17"/>
+      <c r="A184" s="21"/>
       <c r="B184" s="8" t="s">
         <v>9</v>
       </c>
@@ -10392,7 +10567,7 @@
       </c>
     </row>
     <row r="185" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A185" s="17"/>
+      <c r="A185" s="21"/>
       <c r="B185" s="8" t="s">
         <v>10</v>
       </c>
@@ -10443,7 +10618,7 @@
       </c>
     </row>
     <row r="186" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A186" s="17"/>
+      <c r="A186" s="21"/>
       <c r="B186" s="8" t="s">
         <v>11</v>
       </c>
@@ -10494,7 +10669,7 @@
       </c>
     </row>
     <row r="187" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A187" s="17"/>
+      <c r="A187" s="21"/>
       <c r="B187" s="8" t="s">
         <v>12</v>
       </c>
@@ -10545,7 +10720,7 @@
       </c>
     </row>
     <row r="188" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A188" s="17"/>
+      <c r="A188" s="21"/>
       <c r="B188" s="8" t="s">
         <v>13</v>
       </c>
@@ -10596,7 +10771,7 @@
       </c>
     </row>
     <row r="189" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A189" s="17"/>
+      <c r="A189" s="21"/>
       <c r="B189" s="8" t="s">
         <v>14</v>
       </c>
@@ -10647,7 +10822,7 @@
       </c>
     </row>
     <row r="190" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A190" s="17"/>
+      <c r="A190" s="21"/>
       <c r="B190" s="8" t="s">
         <v>15</v>
       </c>
@@ -10698,7 +10873,7 @@
       </c>
     </row>
     <row r="191" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A191" s="17"/>
+      <c r="A191" s="21"/>
       <c r="B191" s="8" t="s">
         <v>16</v>
       </c>
@@ -10749,7 +10924,7 @@
       </c>
     </row>
     <row r="192" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A192" s="17"/>
+      <c r="A192" s="21"/>
       <c r="B192" s="8" t="s">
         <v>17</v>
       </c>
@@ -10800,7 +10975,7 @@
       </c>
     </row>
     <row r="193" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A193" s="17"/>
+      <c r="A193" s="21"/>
       <c r="B193" s="8" t="s">
         <v>18</v>
       </c>
@@ -10851,7 +11026,7 @@
       </c>
     </row>
     <row r="194" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A194" s="17"/>
+      <c r="A194" s="21"/>
       <c r="B194" s="8" t="s">
         <v>19</v>
       </c>
@@ -10902,7 +11077,7 @@
       </c>
     </row>
     <row r="195" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A195" s="17"/>
+      <c r="A195" s="21"/>
       <c r="B195" s="8" t="s">
         <v>20</v>
       </c>
@@ -10953,7 +11128,7 @@
       </c>
     </row>
     <row r="196" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A196" s="17"/>
+      <c r="A196" s="21"/>
       <c r="B196" s="8" t="s">
         <v>21</v>
       </c>
@@ -11004,7 +11179,7 @@
       </c>
     </row>
     <row r="197" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A197" s="17"/>
+      <c r="A197" s="21"/>
       <c r="B197" s="8" t="s">
         <v>22</v>
       </c>
@@ -11055,7 +11230,7 @@
       </c>
     </row>
     <row r="198" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A198" s="17"/>
+      <c r="A198" s="21"/>
       <c r="B198" s="8" t="s">
         <v>23</v>
       </c>
@@ -11106,7 +11281,7 @@
       </c>
     </row>
     <row r="199" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A199" s="17"/>
+      <c r="A199" s="21"/>
       <c r="B199" s="8" t="s">
         <v>24</v>
       </c>
@@ -11157,7 +11332,7 @@
       </c>
     </row>
     <row r="200" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A200" s="17"/>
+      <c r="A200" s="21"/>
       <c r="B200" s="8" t="s">
         <v>25</v>
       </c>
@@ -11208,7 +11383,7 @@
       </c>
     </row>
     <row r="201" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A201" s="17"/>
+      <c r="A201" s="21"/>
       <c r="B201" s="8" t="s">
         <v>26</v>
       </c>
@@ -11259,7 +11434,7 @@
       </c>
     </row>
     <row r="202" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A202" s="17"/>
+      <c r="A202" s="21"/>
       <c r="B202" s="8" t="s">
         <v>27</v>
       </c>
@@ -11310,7 +11485,7 @@
       </c>
     </row>
     <row r="203" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A203" s="17"/>
+      <c r="A203" s="21"/>
       <c r="B203" s="8" t="s">
         <v>28</v>
       </c>
@@ -11361,7 +11536,7 @@
       </c>
     </row>
     <row r="204" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A204" s="17"/>
+      <c r="A204" s="21"/>
       <c r="B204" s="8" t="s">
         <v>29</v>
       </c>
@@ -11412,7 +11587,7 @@
       </c>
     </row>
     <row r="205" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A205" s="17"/>
+      <c r="A205" s="21"/>
       <c r="B205" s="8" t="s">
         <v>30</v>
       </c>
@@ -11463,7 +11638,7 @@
       </c>
     </row>
     <row r="206" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A206" s="17"/>
+      <c r="A206" s="21"/>
       <c r="B206" s="8" t="s">
         <v>31</v>
       </c>
@@ -11514,7 +11689,7 @@
       </c>
     </row>
     <row r="207" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A207" s="17"/>
+      <c r="A207" s="21"/>
       <c r="B207" s="8" t="s">
         <v>32</v>
       </c>
@@ -11565,7 +11740,7 @@
       </c>
     </row>
     <row r="208" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A208" s="17"/>
+      <c r="A208" s="21"/>
       <c r="B208" s="8" t="s">
         <v>33</v>
       </c>
@@ -11616,7 +11791,7 @@
       </c>
     </row>
     <row r="209" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A209" s="17"/>
+      <c r="A209" s="21"/>
       <c r="B209" s="8" t="s">
         <v>34</v>
       </c>
@@ -11667,7 +11842,7 @@
       </c>
     </row>
     <row r="210" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A210" s="17"/>
+      <c r="A210" s="21"/>
       <c r="B210" s="8" t="s">
         <v>35</v>
       </c>
@@ -11718,7 +11893,7 @@
       </c>
     </row>
     <row r="211" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A211" s="17"/>
+      <c r="A211" s="21"/>
       <c r="B211" s="8" t="s">
         <v>36</v>
       </c>
@@ -11769,7 +11944,7 @@
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A212" s="17"/>
+      <c r="A212" s="21"/>
       <c r="B212" s="8" t="s">
         <v>37</v>
       </c>
@@ -11820,7 +11995,7 @@
       </c>
     </row>
     <row r="213" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="18"/>
+      <c r="A213" s="22"/>
       <c r="B213" s="9" t="s">
         <v>38</v>
       </c>
@@ -11871,7 +12046,7 @@
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A214" s="16">
+      <c r="A214" s="20">
         <v>64</v>
       </c>
       <c r="B214" s="11" t="s">
@@ -11924,7 +12099,7 @@
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A215" s="17"/>
+      <c r="A215" s="21"/>
       <c r="B215" s="8" t="s">
         <v>5</v>
       </c>
@@ -11975,7 +12150,7 @@
       </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A216" s="17"/>
+      <c r="A216" s="21"/>
       <c r="B216" s="8" t="s">
         <v>6</v>
       </c>
@@ -12026,7 +12201,7 @@
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A217" s="17"/>
+      <c r="A217" s="21"/>
       <c r="B217" s="8" t="s">
         <v>7</v>
       </c>
@@ -12077,7 +12252,7 @@
       </c>
     </row>
     <row r="218" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A218" s="17"/>
+      <c r="A218" s="21"/>
       <c r="B218" s="8" t="s">
         <v>8</v>
       </c>
@@ -12128,7 +12303,7 @@
       </c>
     </row>
     <row r="219" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A219" s="17"/>
+      <c r="A219" s="21"/>
       <c r="B219" s="8" t="s">
         <v>9</v>
       </c>
@@ -12179,7 +12354,7 @@
       </c>
     </row>
     <row r="220" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A220" s="17"/>
+      <c r="A220" s="21"/>
       <c r="B220" s="8" t="s">
         <v>10</v>
       </c>
@@ -12230,7 +12405,7 @@
       </c>
     </row>
     <row r="221" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A221" s="17"/>
+      <c r="A221" s="21"/>
       <c r="B221" s="8" t="s">
         <v>11</v>
       </c>
@@ -12281,7 +12456,7 @@
       </c>
     </row>
     <row r="222" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A222" s="17"/>
+      <c r="A222" s="21"/>
       <c r="B222" s="8" t="s">
         <v>12</v>
       </c>
@@ -12332,7 +12507,7 @@
       </c>
     </row>
     <row r="223" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A223" s="17"/>
+      <c r="A223" s="21"/>
       <c r="B223" s="8" t="s">
         <v>13</v>
       </c>
@@ -12383,7 +12558,7 @@
       </c>
     </row>
     <row r="224" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A224" s="17"/>
+      <c r="A224" s="21"/>
       <c r="B224" s="8" t="s">
         <v>14</v>
       </c>
@@ -12434,7 +12609,7 @@
       </c>
     </row>
     <row r="225" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A225" s="17"/>
+      <c r="A225" s="21"/>
       <c r="B225" s="8" t="s">
         <v>15</v>
       </c>
@@ -12485,7 +12660,7 @@
       </c>
     </row>
     <row r="226" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A226" s="17"/>
+      <c r="A226" s="21"/>
       <c r="B226" s="8" t="s">
         <v>16</v>
       </c>
@@ -12536,7 +12711,7 @@
       </c>
     </row>
     <row r="227" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A227" s="17"/>
+      <c r="A227" s="21"/>
       <c r="B227" s="8" t="s">
         <v>17</v>
       </c>
@@ -12587,7 +12762,7 @@
       </c>
     </row>
     <row r="228" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A228" s="17"/>
+      <c r="A228" s="21"/>
       <c r="B228" s="8" t="s">
         <v>18</v>
       </c>
@@ -12638,7 +12813,7 @@
       </c>
     </row>
     <row r="229" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A229" s="17"/>
+      <c r="A229" s="21"/>
       <c r="B229" s="8" t="s">
         <v>19</v>
       </c>
@@ -12689,7 +12864,7 @@
       </c>
     </row>
     <row r="230" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A230" s="17"/>
+      <c r="A230" s="21"/>
       <c r="B230" s="8" t="s">
         <v>20</v>
       </c>
@@ -12740,7 +12915,7 @@
       </c>
     </row>
     <row r="231" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A231" s="17"/>
+      <c r="A231" s="21"/>
       <c r="B231" s="8" t="s">
         <v>21</v>
       </c>
@@ -12791,7 +12966,7 @@
       </c>
     </row>
     <row r="232" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A232" s="17"/>
+      <c r="A232" s="21"/>
       <c r="B232" s="8" t="s">
         <v>22</v>
       </c>
@@ -12842,7 +13017,7 @@
       </c>
     </row>
     <row r="233" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A233" s="17"/>
+      <c r="A233" s="21"/>
       <c r="B233" s="8" t="s">
         <v>23</v>
       </c>
@@ -12893,7 +13068,7 @@
       </c>
     </row>
     <row r="234" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A234" s="17"/>
+      <c r="A234" s="21"/>
       <c r="B234" s="8" t="s">
         <v>24</v>
       </c>
@@ -12944,7 +13119,7 @@
       </c>
     </row>
     <row r="235" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A235" s="17"/>
+      <c r="A235" s="21"/>
       <c r="B235" s="8" t="s">
         <v>25</v>
       </c>
@@ -12995,7 +13170,7 @@
       </c>
     </row>
     <row r="236" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A236" s="17"/>
+      <c r="A236" s="21"/>
       <c r="B236" s="8" t="s">
         <v>26</v>
       </c>
@@ -13046,7 +13221,7 @@
       </c>
     </row>
     <row r="237" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A237" s="17"/>
+      <c r="A237" s="21"/>
       <c r="B237" s="8" t="s">
         <v>27</v>
       </c>
@@ -13097,7 +13272,7 @@
       </c>
     </row>
     <row r="238" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A238" s="17"/>
+      <c r="A238" s="21"/>
       <c r="B238" s="8" t="s">
         <v>28</v>
       </c>
@@ -13148,7 +13323,7 @@
       </c>
     </row>
     <row r="239" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A239" s="17"/>
+      <c r="A239" s="21"/>
       <c r="B239" s="8" t="s">
         <v>29</v>
       </c>
@@ -13199,7 +13374,7 @@
       </c>
     </row>
     <row r="240" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A240" s="17"/>
+      <c r="A240" s="21"/>
       <c r="B240" s="8" t="s">
         <v>30</v>
       </c>
@@ -13250,7 +13425,7 @@
       </c>
     </row>
     <row r="241" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A241" s="17"/>
+      <c r="A241" s="21"/>
       <c r="B241" s="8" t="s">
         <v>31</v>
       </c>
@@ -13301,7 +13476,7 @@
       </c>
     </row>
     <row r="242" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A242" s="17"/>
+      <c r="A242" s="21"/>
       <c r="B242" s="8" t="s">
         <v>32</v>
       </c>
@@ -13352,7 +13527,7 @@
       </c>
     </row>
     <row r="243" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A243" s="17"/>
+      <c r="A243" s="21"/>
       <c r="B243" s="8" t="s">
         <v>33</v>
       </c>
@@ -13403,7 +13578,7 @@
       </c>
     </row>
     <row r="244" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A244" s="17"/>
+      <c r="A244" s="21"/>
       <c r="B244" s="8" t="s">
         <v>34</v>
       </c>
@@ -13454,7 +13629,7 @@
       </c>
     </row>
     <row r="245" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A245" s="17"/>
+      <c r="A245" s="21"/>
       <c r="B245" s="8" t="s">
         <v>35</v>
       </c>
@@ -13505,7 +13680,7 @@
       </c>
     </row>
     <row r="246" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A246" s="17"/>
+      <c r="A246" s="21"/>
       <c r="B246" s="8" t="s">
         <v>36</v>
       </c>
@@ -13556,7 +13731,7 @@
       </c>
     </row>
     <row r="247" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A247" s="17"/>
+      <c r="A247" s="21"/>
       <c r="B247" s="8" t="s">
         <v>37</v>
       </c>
@@ -13607,7 +13782,7 @@
       </c>
     </row>
     <row r="248" spans="1:17" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="18"/>
+      <c r="A248" s="22"/>
       <c r="B248" s="9" t="s">
         <v>38</v>
       </c>
@@ -13659,11 +13834,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="O2:Q2"/>
-    <mergeCell ref="L1:Q1"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="A1:A3"/>
     <mergeCell ref="A214:A248"/>
     <mergeCell ref="C1:E2"/>
     <mergeCell ref="F2:H2"/>
@@ -13675,6 +13845,11 @@
     <mergeCell ref="A109:A143"/>
     <mergeCell ref="A144:A178"/>
     <mergeCell ref="A179:A213"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="L1:Q1"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="A1:A3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13695,63 +13870,63 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="16" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="E1" s="25" t="s">
+      <c r="E1" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="19" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="27"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="19" t="s">
+      <c r="F2" s="23"/>
+      <c r="G2" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="21"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18"/>
-      <c r="B3" s="30"/>
-      <c r="C3" s="31"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="32" t="s">
+      <c r="A3" s="22"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G3" s="32" t="s">
+      <c r="G3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="33" t="s">
+      <c r="H3" s="19" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="20" t="s">
         <v>54</v>
       </c>
       <c r="D4" s="11">
@@ -13771,9 +13946,9 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="17"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
       <c r="D5" s="8">
         <v>23</v>
       </c>
@@ -13791,9 +13966,9 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="17"/>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
       <c r="D6" s="8">
         <v>24</v>
       </c>
@@ -13811,9 +13986,9 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
       <c r="D7" s="9">
         <v>25</v>
       </c>
@@ -13831,13 +14006,13 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="20" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="11">
@@ -13846,68 +14021,68 @@
       <c r="E8" s="2">
         <v>318516</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="23" t="s">
         <v>60</v>
       </c>
       <c r="G8" s="2">
         <v>339009</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
+      <c r="A9" s="21"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
       <c r="D9" s="8">
         <v>23</v>
       </c>
       <c r="E9" s="4">
         <v>317723</v>
       </c>
-      <c r="F9" s="29"/>
+      <c r="F9" s="24"/>
       <c r="G9" s="4">
         <v>337765</v>
       </c>
-      <c r="H9" s="29"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
+      <c r="A10" s="21"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
       <c r="D10" s="8">
         <v>24</v>
       </c>
       <c r="E10" s="4">
         <v>330220</v>
       </c>
-      <c r="F10" s="29"/>
+      <c r="F10" s="24"/>
       <c r="G10" s="4">
         <v>334241</v>
       </c>
-      <c r="H10" s="29"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="18"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="9">
         <v>25</v>
       </c>
       <c r="E11" s="10">
         <v>354311</v>
       </c>
-      <c r="F11" s="31"/>
+      <c r="F11" s="25"/>
       <c r="G11" s="10">
         <v>329057</v>
       </c>
-      <c r="H11" s="31"/>
+      <c r="H11" s="25"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="16" t="s">
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20" t="s">
         <v>58</v>
       </c>
       <c r="D12" s="11">
@@ -13916,68 +14091,68 @@
       <c r="E12" s="2">
         <v>311247</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>59</v>
+      <c r="F12" s="23" t="s">
+        <v>60</v>
       </c>
       <c r="G12" s="2">
         <v>327677</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="17"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
       <c r="D13" s="8">
         <v>23</v>
       </c>
       <c r="E13" s="4">
         <v>311709</v>
       </c>
-      <c r="F13" s="29"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="4">
         <v>327774</v>
       </c>
-      <c r="H13" s="29"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="17"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
       <c r="D14" s="8">
         <v>24</v>
       </c>
       <c r="E14" s="4">
         <v>332199</v>
       </c>
-      <c r="F14" s="29"/>
+      <c r="F14" s="24"/>
       <c r="G14" s="4">
         <v>332622</v>
       </c>
-      <c r="H14" s="29"/>
+      <c r="H14" s="24"/>
     </row>
     <row r="15" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="17"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="22"/>
       <c r="D15" s="9">
         <v>25</v>
       </c>
       <c r="E15" s="10">
         <v>350028</v>
       </c>
-      <c r="F15" s="31"/>
+      <c r="F15" s="25"/>
       <c r="G15" s="10">
         <v>330331</v>
       </c>
-      <c r="H15" s="31"/>
+      <c r="H15" s="25"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="17"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="16" t="s">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D16" s="11">
@@ -13997,9 +14172,9 @@
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
       <c r="D17" s="8">
         <v>23</v>
       </c>
@@ -14017,9 +14192,9 @@
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="17"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
       <c r="D18" s="8">
         <v>24</v>
       </c>
@@ -14037,9 +14212,9 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="17"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="22"/>
       <c r="D19" s="9">
         <v>25</v>
       </c>
@@ -14057,9 +14232,9 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="17"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D20" s="11">
@@ -14079,9 +14254,9 @@
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
       <c r="D21" s="8">
         <v>23</v>
       </c>
@@ -14099,9 +14274,9 @@
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
       <c r="D22" s="8">
         <v>24</v>
       </c>
@@ -14119,9 +14294,9 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="22"/>
       <c r="D23" s="9">
         <v>25</v>
       </c>
@@ -14139,9 +14314,9 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="21"/>
+      <c r="B24" s="21"/>
+      <c r="C24" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D24" s="11">
@@ -14161,9 +14336,9 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
       <c r="D25" s="8">
         <v>23</v>
       </c>
@@ -14181,9 +14356,9 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
       <c r="D26" s="8">
         <v>24</v>
       </c>
@@ -14201,9 +14376,9 @@
       </c>
     </row>
     <row r="27" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="22"/>
       <c r="D27" s="9">
         <v>25</v>
       </c>
@@ -14221,9 +14396,9 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="21"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="20" t="s">
         <v>64</v>
       </c>
       <c r="D28" s="11">
@@ -14243,9 +14418,9 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
       <c r="D29" s="8">
         <v>23</v>
       </c>
@@ -14263,9 +14438,9 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
       <c r="D30" s="8">
         <v>24</v>
       </c>
@@ -14283,9 +14458,9 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18"/>
-      <c r="B31" s="18"/>
-      <c r="C31" s="18"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
       <c r="D31" s="9">
         <v>25</v>
       </c>
@@ -14303,13 +14478,13 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+      <c r="A32" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="20" t="s">
         <v>57</v>
       </c>
       <c r="D32" s="11">
@@ -14318,68 +14493,68 @@
       <c r="E32" s="2">
         <v>376391</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="23" t="s">
         <v>59</v>
       </c>
       <c r="G32" s="2">
         <v>442823</v>
       </c>
-      <c r="H32" s="21" t="s">
+      <c r="H32" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
       <c r="D33" s="8">
         <v>23</v>
       </c>
       <c r="E33" s="4">
         <v>374327</v>
       </c>
-      <c r="F33" s="29"/>
+      <c r="F33" s="24"/>
       <c r="G33" s="4">
         <v>448196</v>
       </c>
-      <c r="H33" s="29"/>
+      <c r="H33" s="24"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
       <c r="D34" s="8">
         <v>24</v>
       </c>
       <c r="E34" s="4">
         <v>384219</v>
       </c>
-      <c r="F34" s="29"/>
+      <c r="F34" s="24"/>
       <c r="G34" s="4">
         <v>440043</v>
       </c>
-      <c r="H34" s="29"/>
+      <c r="H34" s="24"/>
     </row>
     <row r="35" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="22"/>
       <c r="D35" s="9">
         <v>25</v>
       </c>
       <c r="E35" s="10">
         <v>404669</v>
       </c>
-      <c r="F35" s="31"/>
+      <c r="F35" s="25"/>
       <c r="G35" s="10">
         <v>428171</v>
       </c>
-      <c r="H35" s="31"/>
+      <c r="H35" s="25"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="16" t="s">
+      <c r="A36" s="21"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="20" t="s">
         <v>58</v>
       </c>
       <c r="D36" s="11">
@@ -14388,68 +14563,68 @@
       <c r="E36" s="2">
         <v>384118</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="23" t="s">
         <v>59</v>
       </c>
       <c r="G36" s="2">
         <v>440991</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H36" s="23" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
+      <c r="A37" s="21"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21"/>
       <c r="D37" s="8">
         <v>23</v>
       </c>
       <c r="E37" s="4">
         <v>374096</v>
       </c>
-      <c r="F37" s="29"/>
+      <c r="F37" s="24"/>
       <c r="G37" s="4">
         <v>444691</v>
       </c>
-      <c r="H37" s="29"/>
+      <c r="H37" s="24"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
       <c r="D38" s="8">
         <v>24</v>
       </c>
       <c r="E38" s="4">
         <v>384210</v>
       </c>
-      <c r="F38" s="29"/>
+      <c r="F38" s="24"/>
       <c r="G38" s="4">
         <v>431463</v>
       </c>
-      <c r="H38" s="29"/>
+      <c r="H38" s="24"/>
     </row>
     <row r="39" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="18"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="22"/>
       <c r="D39" s="9">
         <v>25</v>
       </c>
       <c r="E39" s="10">
         <v>403381</v>
       </c>
-      <c r="F39" s="31"/>
+      <c r="F39" s="25"/>
       <c r="G39" s="10">
         <v>418758</v>
       </c>
-      <c r="H39" s="31"/>
+      <c r="H39" s="25"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="16" t="s">
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="20" t="s">
         <v>61</v>
       </c>
       <c r="D40" s="11">
@@ -14469,9 +14644,9 @@
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
       <c r="D41" s="8">
         <v>23</v>
       </c>
@@ -14489,9 +14664,9 @@
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
+      <c r="A42" s="21"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="21"/>
       <c r="D42" s="8">
         <v>24</v>
       </c>
@@ -14509,9 +14684,9 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="18"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="22"/>
       <c r="D43" s="9">
         <v>25</v>
       </c>
@@ -14529,9 +14704,9 @@
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="16" t="s">
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="20" t="s">
         <v>62</v>
       </c>
       <c r="D44" s="11">
@@ -14551,9 +14726,9 @@
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
       <c r="D45" s="8">
         <v>23</v>
       </c>
@@ -14571,9 +14746,9 @@
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
       <c r="D46" s="8">
         <v>24</v>
       </c>
@@ -14591,9 +14766,9 @@
       </c>
     </row>
     <row r="47" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="18"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="22"/>
       <c r="D47" s="9">
         <v>25</v>
       </c>
@@ -14611,9 +14786,9 @@
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="16" t="s">
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="20" t="s">
         <v>63</v>
       </c>
       <c r="D48" s="11">
@@ -14633,9 +14808,9 @@
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="17"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="17"/>
+      <c r="A49" s="21"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="21"/>
       <c r="D49" s="8">
         <v>23</v>
       </c>
@@ -14653,9 +14828,9 @@
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
+      <c r="A50" s="21"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
       <c r="D50" s="8">
         <v>24</v>
       </c>
@@ -14673,9 +14848,9 @@
       </c>
     </row>
     <row r="51" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="17"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18"/>
+      <c r="A51" s="21"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="22"/>
       <c r="D51" s="9">
         <v>25</v>
       </c>
@@ -14693,9 +14868,9 @@
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="17"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="16" t="s">
+      <c r="A52" s="21"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="20" t="s">
         <v>64</v>
       </c>
       <c r="D52" s="11">
@@ -14715,9 +14890,9 @@
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="17"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
       <c r="D53" s="8">
         <v>23</v>
       </c>
@@ -14735,9 +14910,9 @@
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="17"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
       <c r="D54" s="8">
         <v>24</v>
       </c>
@@ -14755,9 +14930,9 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="18"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
       <c r="D55" s="9">
         <v>25</v>
       </c>
@@ -14776,6 +14951,27 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="E1:H1"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="B1:C3"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="C4:C7"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="A8:A31"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="F12:F15"/>
+    <mergeCell ref="H12:H15"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="C24:C27"/>
+    <mergeCell ref="C28:C31"/>
+    <mergeCell ref="B8:B31"/>
     <mergeCell ref="A32:A55"/>
     <mergeCell ref="F32:F35"/>
     <mergeCell ref="F36:F39"/>
@@ -14788,27 +14984,246 @@
     <mergeCell ref="C44:C47"/>
     <mergeCell ref="C48:C51"/>
     <mergeCell ref="C52:C55"/>
-    <mergeCell ref="C16:C19"/>
-    <mergeCell ref="C20:C23"/>
-    <mergeCell ref="C24:C27"/>
-    <mergeCell ref="C28:C31"/>
-    <mergeCell ref="B8:B31"/>
-    <mergeCell ref="A8:A31"/>
-    <mergeCell ref="C12:C15"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="F12:F15"/>
-    <mergeCell ref="H12:H15"/>
-    <mergeCell ref="A4:A7"/>
-    <mergeCell ref="B1:C3"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="C4:C7"/>
-    <mergeCell ref="B4:B7"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="E1:H1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40284002-38DE-493E-996F-1BC2A8A601F3}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.5546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="5.77734375" style="36" customWidth="1"/>
+    <col min="5" max="5" width="10.77734375" style="36" customWidth="1"/>
+    <col min="6" max="7" width="6.77734375" style="36" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="36" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="23"/>
+      <c r="E1" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="23"/>
+      <c r="H1" s="16" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="50">
+        <v>54.5</v>
+      </c>
+      <c r="D3" s="51">
+        <v>59.4</v>
+      </c>
+      <c r="E3" s="52">
+        <v>63.3</v>
+      </c>
+      <c r="F3" s="50">
+        <v>2120</v>
+      </c>
+      <c r="G3" s="51">
+        <v>2280</v>
+      </c>
+      <c r="H3" s="52">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="54">
+        <v>53.7</v>
+      </c>
+      <c r="D4" s="55">
+        <v>60.1</v>
+      </c>
+      <c r="E4" s="56">
+        <v>58.6</v>
+      </c>
+      <c r="F4" s="54">
+        <v>1460</v>
+      </c>
+      <c r="G4" s="55">
+        <v>1610</v>
+      </c>
+      <c r="H4" s="56">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="21"/>
+      <c r="B5" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="44">
+        <v>53.4</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="46">
+        <v>58.7</v>
+      </c>
+      <c r="F5" s="44">
+        <v>1450</v>
+      </c>
+      <c r="G5" s="38" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="46">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="22"/>
+      <c r="B6" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="45">
+        <v>45.7</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="47">
+        <v>57.4</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="53" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="54">
+        <v>74.2</v>
+      </c>
+      <c r="D7" s="55">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="E7" s="56">
+        <v>86.3</v>
+      </c>
+      <c r="F7" s="54">
+        <v>1670</v>
+      </c>
+      <c r="G7" s="55">
+        <v>1880</v>
+      </c>
+      <c r="H7" s="56">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="57"/>
+      <c r="B8" s="58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C8" s="59">
+        <v>73.2</v>
+      </c>
+      <c r="D8" s="60">
+        <v>83</v>
+      </c>
+      <c r="E8" s="61">
+        <v>88.6</v>
+      </c>
+      <c r="F8" s="59">
+        <v>1680</v>
+      </c>
+      <c r="G8" s="60">
+        <v>1880</v>
+      </c>
+      <c r="H8" s="61">
+        <v>1620</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="62" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="63"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="62" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="63"/>
+      <c r="H9" s="48" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
